--- a/naver-place-crawler/results_nail/광주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/광주_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -850,6 +850,680 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>아미네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>choitattoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1403-7234</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>광주 광산구 장신로147번길 5-8 삼우주차빌딩 1층 아미네일</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/choitattoo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wccs34</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1553</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>796</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2349</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>311449057</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/311449057</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>탑티어네일 상무점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>psy1481@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>062-372-7775</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>광주 서구 상무중앙로 57 상무 S클래스 상가 1층 , 112호</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/toptier_nail.sm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2584</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2639</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1392531564</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1392531564</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>우아한네일</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kqw1230@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1472-3402</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>광주 서구 상무화원로 12 1층 우아한네일</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wooahan_nail</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>211</v>
+      </c>
+      <c r="R7" t="n">
+        <v>668</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1384925755</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1384925755</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>리보니 오로지푸스 무좀 내성발톱 발각질 맞춤깔창</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rebornee__@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1388-0801</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>광주 남구 대남대로283번길 8 1층</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rebornee__</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w1hn</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>288</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1375528945</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375528945</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>르벨라네일 광주화정점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1382-2073</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>광주 서구 화운로 136 르벨라네일</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebella_nail_?igsh=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tn50</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>205</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1010542672</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010542672</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>율리스네일 쌍촌점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ajgktka1@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1346-8302</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>광주 서구 상무오월로3번길 32-7 1층 율리스네일</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yullys_nail</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weyd58z</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>18</v>
+      </c>
+      <c r="R10" t="n">
+        <v>189</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1977590645</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1977590645</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>모나코네일</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>theom2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1417-1157</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>광주 서구 백석길 4 새마을금고옆 1층 (리젠시빌주택건물)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/_monaconail_</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h6x7</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>71</v>
+      </c>
+      <c r="R11" t="n">
+        <v>369</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>820466324</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/820466324</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_nail/광주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/광주_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="Q2" t="n">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일플롯 광주첨단점</t>
+          <t>네일홀릭 학동본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nailflot@naver.com</t>
+          <t>nailholicshop@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1377-2701</t>
+          <t>0507-1334-0423</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로826번길 47 2층 201호 네일플롯</t>
+          <t>광주 동구 학소로 125 105호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/flot_nail</t>
+          <t>https://blog.naver.com/nailholicshop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,22 +699,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47h6j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2111</v>
+        <v>83</v>
       </c>
       <c r="Q3" t="n">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>2288</v>
+        <v>91</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1760350557</t>
+          <t>34079967</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760350557</t>
+          <t>https://m.place.naver.com/place/34079967</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호시네일 광주상무점</t>
+          <t>네일플롯 광주첨단점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jiwon4348@naver.com</t>
+          <t>nailflot@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1373-4330</t>
+          <t>0507-1377-2701</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 서구 상무시민로 131 3층</t>
+          <t>광주 광산구 임방울대로826번길 47 2층 201호 네일플롯</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hosinail_</t>
+          <t>http://www.instagram.com/flot_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o5td</t>
+          <t>https://talk.naver.com/ct/w47h6j</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1832</v>
+        <v>2111</v>
       </c>
       <c r="Q4" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="R4" t="n">
-        <v>2001</v>
+        <v>2288</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1367173612</t>
+          <t>1760350557</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1367173612</t>
+          <t>https://m.place.naver.com/place/1760350557</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아미네일</t>
+          <t>호시네일 광주상무점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>choitattoo@naver.com</t>
+          <t>jiwon4348@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1403-7234</t>
+          <t>0507-1373-4330</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 광산구 장신로147번길 5-8 삼우주차빌딩 1층 아미네일</t>
+          <t>광주 서구 상무시민로 131 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/choitattoo</t>
+          <t>https://www.instagram.com/hosinail_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccs34</t>
+          <t>https://talk.naver.com/ct/w4o5td</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1553</v>
+        <v>1832</v>
       </c>
       <c r="Q5" t="n">
-        <v>796</v>
+        <v>169</v>
       </c>
       <c r="R5" t="n">
-        <v>2349</v>
+        <v>2001</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>311449057</t>
+          <t>1367173612</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/311449057</t>
+          <t>https://m.place.naver.com/place/1367173612</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>탑티어네일 상무점</t>
+          <t>아미네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>psy1481@naver.com</t>
+          <t>choitattoo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>062-372-7775</t>
+          <t>0507-1403-7234</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 57 상무 S클래스 상가 1층 , 112호</t>
+          <t>광주 광산구 장신로147번길 5-8 삼우주차빌딩 1층 아미네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/toptier_nail.sm</t>
+          <t>https://blog.naver.com/choitattoo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wccs34</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2584</v>
+        <v>1553</v>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>797</v>
       </c>
       <c r="R6" t="n">
-        <v>2639</v>
+        <v>2350</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1392531564</t>
+          <t>311449057</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1392531564</t>
+          <t>https://m.place.naver.com/place/311449057</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>우아한네일</t>
+          <t>탑티어네일 상무점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kqw1230@naver.com</t>
+          <t>psy1481@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1472-3402</t>
+          <t>062-372-7775</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 서구 상무화원로 12 1층 우아한네일</t>
+          <t>광주 서구 상무중앙로 57 상무 S클래스 상가 1층 , 112호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wooahan_nail</t>
+          <t>http://www.instagram.com/toptier_nail.sm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>457</v>
+        <v>2585</v>
       </c>
       <c r="Q7" t="n">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="R7" t="n">
-        <v>668</v>
+        <v>2640</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1384925755</t>
+          <t>1392531564</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1384925755</t>
+          <t>https://m.place.naver.com/place/1392531564</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1242,30 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>르벨라네일 광주화정점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>아임뷰티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>wldyd3412@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1382-2073</t>
+          <t>0507-1328-6485</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 화운로 136 르벨라네일</t>
+          <t>광주 광산구 앰코로 35 3층 312-1호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lebella_nail_?igsh=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://www.instagram.com/im_beauty_nail_?igsh=cGY0b3Bhano0dzR5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tn50</t>
+          <t>https://talk.naver.com/ct/w49mnk</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="R9" t="n">
-        <v>205</v>
+        <v>381</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1010542672</t>
+          <t>1323398142</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010542672</t>
+          <t>https://m.place.naver.com/place/1323398142</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1340,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>율리스네일 쌍촌점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ajgktka1@naver.com</t>
-        </is>
-      </c>
+          <t>르벨라네일 광주화정점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1346-8302</t>
+          <t>0507-1382-2073</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 상무오월로3번길 32-7 1층 율리스네일</t>
+          <t>광주 서구 화운로 136 르벨라네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yullys_nail</t>
+          <t>https://www.instagram.com/lebella_nail_?igsh=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/weyd58z</t>
+          <t>https://talk.naver.com/ct/w5tn50</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1977590645</t>
+          <t>1010542672</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1977590645</t>
+          <t>https://m.place.naver.com/place/1010542672</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_nail/광주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/광주_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일더빛나 페디크루 광주전대점 내성발톱 무좀 발각질</t>
+          <t>네일홀릭 학동본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jisu1980@naver.com</t>
+          <t>nailholicshop@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1399-3236</t>
+          <t>0507-1334-0423</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 북구 서방로9번길 12 2층 네일더빛나 전대점</t>
+          <t>광주 동구 학소로 125 105호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jisu1980</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dwzd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1167</v>
+        <v>83</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>2119</v>
+        <v>91</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1824211380</t>
+          <t>34079967</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824211380</t>
+          <t>https://m.place.naver.com/place/34079967</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일홀릭 학동본점</t>
+          <t>네일플롯 광주첨단점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nailholicshop@naver.com</t>
+          <t>nailflot@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1334-0423</t>
+          <t>0507-1377-2701</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 동구 학소로 125 105호</t>
+          <t>광주 광산구 임방울대로826번길 47 2층 201호 네일플롯</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailholicshop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,23 +690,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47h6j</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>83</v>
+        <v>2112</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="R3" t="n">
-        <v>91</v>
+        <v>2289</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>34079967</t>
+          <t>1760350557</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34079967</t>
+          <t>https://m.place.naver.com/place/1760350557</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일플롯 광주첨단점</t>
+          <t>네일더빛나 페디크루 광주전대점 내성발톱 무좀 발각질</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nailflot@naver.com</t>
+          <t>jisu1980@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1377-2701</t>
+          <t>0507-1399-3236</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로826번길 47 2층 201호 네일플롯</t>
+          <t>광주 북구 서방로9번길 12 2층 네일더빛나 전대점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/flot_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47h6j</t>
+          <t>https://talk.naver.com/ct/w4dwzd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2111</v>
+        <v>1167</v>
       </c>
       <c r="Q4" t="n">
-        <v>177</v>
+        <v>953</v>
       </c>
       <c r="R4" t="n">
-        <v>2288</v>
+        <v>2120</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1760350557</t>
+          <t>1824211380</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760350557</t>
+          <t>https://m.place.naver.com/place/1824211380</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hosinail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1016,10 @@
         <v>1553</v>
       </c>
       <c r="Q6" t="n">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="R6" t="n">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리보니 오로지푸스 무좀 내성발톱 발각질 맞춤깔창</t>
+          <t>우아한네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rebornee__@naver.com</t>
+          <t>kqw1230@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-0801</t>
+          <t>0507-1472-3402</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 남구 대남대로283번길 8 1층</t>
+          <t>광주 서구 상무화원로 12 1층 우아한네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rebornee__</t>
+          <t>https://www.instagram.com/wooahan_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,19 +1181,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w1hn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>243</v>
+        <v>457</v>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>211</v>
       </c>
       <c r="R8" t="n">
-        <v>288</v>
+        <v>668</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1375528945</t>
+          <t>1384925755</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375528945</t>
+          <t>https://m.place.naver.com/place/1384925755</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1238,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아임뷰티</t>
+          <t>리보니 오로지푸스 무좀 내성발톱 발각질 맞춤깔창</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wldyd3412@naver.com</t>
+          <t>rebornee__@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1328-6485</t>
+          <t>0507-1388-0801</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 앰코로 35 3층 312-1호</t>
+          <t>광주 남구 대남대로283번길 8 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/im_beauty_nail_?igsh=cGY0b3Bhano0dzR5</t>
+          <t>https://blog.naver.com/rebornee__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49mnk</t>
+          <t>https://talk.naver.com/ct/w5w1hn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="R9" t="n">
-        <v>381</v>
+        <v>288</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1323398142</t>
+          <t>1375528945</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323398142</t>
+          <t>https://m.place.naver.com/place/1375528945</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1516,101 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>원하다뷰티</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>moonda09120@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>광주 광산구 산월로 17 1층 원하다뷰티</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w436o4</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>515</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1007616332</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1007616332</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
